--- a/Templates/Strategic planning/IC-Internal-Audit-Risk-Register-9419.xlsx
+++ b/Templates/Strategic planning/IC-Internal-Audit-Risk-Register-9419.xlsx
@@ -8,9 +8,9 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Internal Audit Risk Register" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Scale" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="- Disclaimer -" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Internal Audit Risk Register" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Scale" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="- Disclaimer -" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Internal Audit Risk Register'!$B$2:$L$24</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t xml:space="preserve">INTERNAL AUDIT RISK REGISTER TEMPLATE</t>
   </si>
@@ -136,6 +136,9 @@
     <t xml:space="preserve">FAST</t>
   </si>
   <si>
+    <t xml:space="preserve">Compliance</t>
+  </si>
+  <si>
     <t xml:space="preserve">Operational</t>
   </si>
   <si>
@@ -143,9 +146,6 @@
   </si>
   <si>
     <t xml:space="preserve">MODERATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compliance</t>
   </si>
   <si>
     <t xml:space="preserve">Social media policy not enforced</t>
@@ -771,288 +771,280 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="69">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="11" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="12" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="13" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="12" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="12" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="13" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="12" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="12" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="14" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="11" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="12" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="13" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="6" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="12" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="12" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="13" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="12" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="12" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="14" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="23" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="23" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1192,9 +1184,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1422000</xdr:colOff>
+      <xdr:colOff>1421640</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2501640</xdr:rowOff>
+      <xdr:rowOff>2501280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1210,7 +1202,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="12420360" cy="2501640"/>
+          <a:ext cx="11265480" cy="2501280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1231,9 +1223,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>12240</xdr:colOff>
+      <xdr:colOff>11880</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>198720</xdr:rowOff>
+      <xdr:rowOff>198360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1246,8 +1238,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17100360" y="2559240"/>
-          <a:ext cx="4213080" cy="2916360"/>
+          <a:off x="15480000" y="2559240"/>
+          <a:ext cx="3597120" cy="2916000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1262,8 +1254,114 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF8497B0"/>
     <pageSetUpPr fitToPage="true"/>
@@ -1271,44 +1369,44 @@
   <dimension ref="B1:T26"/>
   <sheetFormatPr defaultColWidth="11.0078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="22.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="3" width="22.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="37.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="3.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="3.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="3.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="22.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="3.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="3.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="22.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="22.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="4" width="22.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="37.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="3.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="3.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="3.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="22.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="3.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="3.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="2" s="4" customFormat="true" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="5" t="s">
+    <row r="2" s="5" customFormat="true" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-    </row>
-    <row r="3" s="8" customFormat="true" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+    </row>
+    <row r="3" s="1" customFormat="true" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
@@ -1323,7 +1421,7 @@
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
     </row>
-    <row r="4" s="8" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
@@ -1336,7 +1434,7 @@
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
     </row>
-    <row r="5" s="8" customFormat="true" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" s="1" customFormat="true" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
         <v>2</v>
       </c>
@@ -1351,7 +1449,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
     </row>
-    <row r="6" s="8" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11"/>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -1364,7 +1462,7 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
     </row>
-    <row r="7" s="8" customFormat="true" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" s="1" customFormat="true" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
         <v>3</v>
       </c>
@@ -1379,7 +1477,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
     </row>
-    <row r="8" s="8" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
@@ -1494,14 +1592,14 @@
         <v>28</v>
       </c>
       <c r="F11" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="27" t="n">
         <f aca="false">IF(F11*G11=0,"",F11*G11)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" s="25"/>
       <c r="J11" s="25"/>
@@ -1518,40 +1616,42 @@
         <v>1</v>
       </c>
       <c r="Q11" s="31"/>
-      <c r="R11" s="32" t="s">
+      <c r="R11" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="T11" s="33" t="s">
+      <c r="T11" s="32" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="36" t="str">
+      <c r="B12" s="33"/>
+      <c r="C12" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="35" t="str">
         <f aca="false">IF(F12*G12=0,"",F12*G12)</f>
         <v/>
       </c>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="37"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="36"/>
       <c r="N12" s="29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P12" s="30" t="n">
         <v>2</v>
       </c>
       <c r="Q12" s="31"/>
-      <c r="R12" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="T12" s="38" t="s">
+      <c r="R12" s="25" t="s">
         <v>35</v>
+      </c>
+      <c r="T12" s="37" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1561,7 +1661,7 @@
       <c r="E13" s="25"/>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
-      <c r="H13" s="39" t="str">
+      <c r="H13" s="27" t="str">
         <f aca="false">IF(F13*G13=0,"",F13*G13)</f>
         <v/>
       </c>
@@ -1570,34 +1670,34 @@
       <c r="K13" s="25"/>
       <c r="L13" s="28"/>
       <c r="N13" s="29" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P13" s="30" t="n">
         <v>3</v>
       </c>
       <c r="Q13" s="31"/>
-      <c r="R13" s="32" t="s">
+      <c r="R13" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="T13" s="40" t="s">
+      <c r="T13" s="38" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="36" t="str">
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="35" t="str">
         <f aca="false">IF(F14*G14=0,"",F14*G14)</f>
         <v/>
       </c>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="37"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="36"/>
       <c r="N14" s="29" t="s">
         <v>38</v>
       </c>
@@ -1605,7 +1705,7 @@
         <v>4</v>
       </c>
       <c r="Q14" s="31"/>
-      <c r="R14" s="32" t="s">
+      <c r="R14" s="25" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1616,7 +1716,7 @@
       <c r="E15" s="25"/>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
-      <c r="H15" s="39" t="str">
+      <c r="H15" s="27" t="str">
         <f aca="false">IF(F15*G15=0,"",F15*G15)</f>
         <v/>
       </c>
@@ -1631,29 +1731,29 @@
         <v>5</v>
       </c>
       <c r="Q15" s="31"/>
-      <c r="R15" s="32" t="s">
+      <c r="R15" s="25" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36" t="str">
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="35" t="str">
         <f aca="false">IF(F16*G16=0,"",F16*G16)</f>
         <v/>
       </c>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="37"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="36"/>
       <c r="N16" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="R16" s="32" t="s">
+      <c r="R16" s="25" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1664,7 +1764,7 @@
       <c r="E17" s="25"/>
       <c r="F17" s="26"/>
       <c r="G17" s="26"/>
-      <c r="H17" s="39" t="str">
+      <c r="H17" s="27" t="str">
         <f aca="false">IF(F17*G17=0,"",F17*G17)</f>
         <v/>
       </c>
@@ -1678,21 +1778,21 @@
       <c r="R17" s="29"/>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="36" t="str">
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="35" t="str">
         <f aca="false">IF(F18*G18=0,"",F18*G18)</f>
         <v/>
       </c>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="37"/>
-      <c r="N18" s="32"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="36"/>
+      <c r="N18" s="25"/>
       <c r="R18" s="29"/>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1702,7 +1802,7 @@
       <c r="E19" s="25"/>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
-      <c r="H19" s="39" t="str">
+      <c r="H19" s="27" t="str">
         <f aca="false">IF(F19*G19=0,"",F19*G19)</f>
         <v/>
       </c>
@@ -1710,24 +1810,24 @@
       <c r="J19" s="25"/>
       <c r="K19" s="25"/>
       <c r="L19" s="28"/>
-      <c r="N19" s="32"/>
+      <c r="N19" s="25"/>
       <c r="R19" s="29"/>
     </row>
     <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="36" t="str">
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="35" t="str">
         <f aca="false">IF(F20*G20=0,"",F20*G20)</f>
         <v/>
       </c>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="37"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="25"/>
@@ -1736,7 +1836,7 @@
       <c r="E21" s="25"/>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
-      <c r="H21" s="39" t="str">
+      <c r="H21" s="27" t="str">
         <f aca="false">IF(F21*G21=0,"",F21*G21)</f>
         <v/>
       </c>
@@ -1746,20 +1846,20 @@
       <c r="L21" s="28"/>
     </row>
     <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="36" t="str">
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="35" t="str">
         <f aca="false">IF(F22*G22=0,"",F22*G22)</f>
         <v/>
       </c>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="37"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="36"/>
     </row>
     <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="25"/>
@@ -1768,7 +1868,7 @@
       <c r="E23" s="25"/>
       <c r="F23" s="26"/>
       <c r="G23" s="26"/>
-      <c r="H23" s="39" t="str">
+      <c r="H23" s="27" t="str">
         <f aca="false">IF(F23*G23=0,"",F23*G23)</f>
         <v/>
       </c>
@@ -1778,35 +1878,35 @@
       <c r="L23" s="28"/>
     </row>
     <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="43" t="str">
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="41" t="str">
         <f aca="false">IF(F24*G24=0,"",F24*G24)</f>
         <v/>
       </c>
-      <c r="I24" s="41"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="44"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="42"/>
     </row>
     <row r="26" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="45"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1876,7 +1976,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFADB9CA"/>
     <pageSetUpPr fitToPage="true"/>
@@ -1884,149 +1984,149 @@
   <dimension ref="B1:H13"/>
   <sheetFormatPr defaultColWidth="11.0078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="7.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="7.5"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="true" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="46" t="s">
+    <row r="1" s="5" customFormat="true" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="44" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="48" t="n">
+      <c r="C2" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="49" t="n">
+      <c r="D2" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="50" t="n">
+      <c r="E2" s="48" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="51" t="n">
+      <c r="F2" s="49" t="n">
         <v>15</v>
       </c>
-      <c r="G2" s="51" t="n">
+      <c r="G2" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="H2" s="52" t="n">
+      <c r="H2" s="50" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="47"/>
-      <c r="C3" s="53" t="n">
+      <c r="B3" s="45"/>
+      <c r="C3" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="D3" s="54" t="n">
+      <c r="D3" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="55" t="n">
+      <c r="E3" s="53" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="55" t="n">
+      <c r="F3" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="G3" s="56" t="n">
+      <c r="G3" s="54" t="n">
         <v>16</v>
       </c>
-      <c r="H3" s="57" t="n">
+      <c r="H3" s="55" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="47"/>
-      <c r="C4" s="53" t="n">
+      <c r="B4" s="45"/>
+      <c r="C4" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="54" t="n">
+      <c r="D4" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="55" t="n">
+      <c r="E4" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="55" t="n">
+      <c r="F4" s="53" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="55" t="n">
+      <c r="G4" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="H4" s="57" t="n">
+      <c r="H4" s="55" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="47"/>
-      <c r="C5" s="53" t="n">
+      <c r="B5" s="45"/>
+      <c r="C5" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="54" t="n">
+      <c r="D5" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="58" t="n">
+      <c r="E5" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="55" t="n">
+      <c r="F5" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="55" t="n">
+      <c r="G5" s="53" t="n">
         <v>8</v>
       </c>
-      <c r="H5" s="59" t="n">
+      <c r="H5" s="57" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="47"/>
-      <c r="C6" s="60" t="n">
+      <c r="B6" s="45"/>
+      <c r="C6" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="n">
+      <c r="D6" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="62" t="n">
+      <c r="E6" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="62" t="n">
+      <c r="F6" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="62" t="n">
+      <c r="G6" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="63" t="n">
+      <c r="H6" s="61" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C7" s="64"/>
-      <c r="D7" s="65" t="n">
+      <c r="C7" s="62"/>
+      <c r="D7" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="66" t="n">
+      <c r="E7" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="66" t="n">
+      <c r="F7" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="66" t="n">
+      <c r="G7" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="67" t="n">
+      <c r="H7" s="65" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D8" s="68" t="s">
+      <c r="D8" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2048,7 +2148,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF404040"/>
     <pageSetUpPr fitToPage="false"/>
@@ -2056,13 +2156,13 @@
   <dimension ref="B2"/>
   <sheetFormatPr defaultColWidth="10.83984375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="69" width="3.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="69" width="88.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="3" style="69" width="10.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="67" width="3.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="67" width="88.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="3" style="67" width="10.83"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="68" t="s">
         <v>47</v>
       </c>
     </row>
